--- a/Day4_Excel_Basics.xlsx
+++ b/Day4_Excel_Basics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k.omkari\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{87D0217E-345B-43BA-AAAE-7AC2FA3CDFAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75EE558B-3F3F-4B0B-A19B-6967EDC243D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="101">
   <si>
     <t>Date</t>
   </si>
@@ -39,9 +39,6 @@
     <t>Client</t>
   </si>
   <si>
-    <t>Contact</t>
-  </si>
-  <si>
     <t>Department</t>
   </si>
   <si>
@@ -81,9 +78,6 @@
     <t>THE PROCTER &amp; GAMBLE COMPANY (XNYS:PG)</t>
   </si>
   <si>
-    <t>Nyla Novak</t>
-  </si>
-  <si>
     <t>Operations_Florida</t>
   </si>
   <si>
@@ -105,18 +99,12 @@
     <t>BANK OF AMERICA CORPORATION (XNYS:BAC)</t>
   </si>
   <si>
-    <t>Kylee Townsend</t>
-  </si>
-  <si>
     <t>Card</t>
   </si>
   <si>
     <t>WALMART INC. (XNYS:WMT)</t>
   </si>
   <si>
-    <t>Nora Rollins</t>
-  </si>
-  <si>
     <t>TARGET CORPORATION (XNYS:TGT)</t>
   </si>
   <si>
@@ -132,9 +120,6 @@
     <t>EXXON MOBIL CORPORATION (XNYS:XOM)</t>
   </si>
   <si>
-    <t>Lucia Mckay</t>
-  </si>
-  <si>
     <t>VERIZON COMMUNICATIONS INC. (XNYS:VZ)</t>
   </si>
   <si>
@@ -177,76 +162,178 @@
     <t>LOCKHEED MARTIN CORPORATION (XNYS:LMT)</t>
   </si>
   <si>
-    <t>Mik Naam</t>
-  </si>
-  <si>
-    <t>Bill Smith</t>
-  </si>
-  <si>
-    <t>Ken Singh</t>
-  </si>
-  <si>
-    <t>Harley Fritz</t>
-  </si>
-  <si>
-    <t>David Rasmussen</t>
-  </si>
-  <si>
-    <t>Ivan Hiney</t>
-  </si>
-  <si>
-    <t>Jonha Ma</t>
-  </si>
-  <si>
-    <t>Jordan Boone</t>
-  </si>
-  <si>
-    <t>Brendan Wallace</t>
-  </si>
-  <si>
-    <t>Conor Wise</t>
-  </si>
-  <si>
-    <t>Steven Michael</t>
-  </si>
-  <si>
-    <t>Jose Roach</t>
-  </si>
-  <si>
-    <t>Franklin Wrigt</t>
-  </si>
-  <si>
-    <t>Alia Thornton</t>
-  </si>
-  <si>
-    <t>Denzel Flores</t>
-  </si>
-  <si>
-    <t>Bruno Cordova</t>
-  </si>
-  <si>
-    <t>Jaylynn Napp</t>
-  </si>
-  <si>
-    <t>Bruce Rich</t>
-  </si>
-  <si>
-    <t>Arturo Moore</t>
-  </si>
-  <si>
-    <t>Bryce Carpenter</t>
-  </si>
-  <si>
-    <t>Jaidyn Andersen</t>
-  </si>
-  <si>
-    <t>Mark Walm</t>
-  </si>
-  <si>
-    <t>Harry Lee</t>
-  </si>
-  <si>
-    <t>Josh Johnson</t>
+    <t>Bill</t>
+  </si>
+  <si>
+    <t>Smith</t>
+  </si>
+  <si>
+    <t>Ken</t>
+  </si>
+  <si>
+    <t>Singh</t>
+  </si>
+  <si>
+    <t>Harley</t>
+  </si>
+  <si>
+    <t>Fritz</t>
+  </si>
+  <si>
+    <t>Nyla</t>
+  </si>
+  <si>
+    <t>Novak</t>
+  </si>
+  <si>
+    <t>David</t>
+  </si>
+  <si>
+    <t>Rasmussen</t>
+  </si>
+  <si>
+    <t>Ivan</t>
+  </si>
+  <si>
+    <t>Hiney</t>
+  </si>
+  <si>
+    <t>Jonha</t>
+  </si>
+  <si>
+    <t>Ma</t>
+  </si>
+  <si>
+    <t>Jordan</t>
+  </si>
+  <si>
+    <t>Boone</t>
+  </si>
+  <si>
+    <t>Kylee</t>
+  </si>
+  <si>
+    <t>Townsend</t>
+  </si>
+  <si>
+    <t>Nora</t>
+  </si>
+  <si>
+    <t>Rollins</t>
+  </si>
+  <si>
+    <t>Brendan</t>
+  </si>
+  <si>
+    <t>Wallace</t>
+  </si>
+  <si>
+    <t>Conor</t>
+  </si>
+  <si>
+    <t>Wise</t>
+  </si>
+  <si>
+    <t>Steven</t>
+  </si>
+  <si>
+    <t>Michael</t>
+  </si>
+  <si>
+    <t>Lucia</t>
+  </si>
+  <si>
+    <t>Mckay</t>
+  </si>
+  <si>
+    <t>Jose</t>
+  </si>
+  <si>
+    <t>Roach</t>
+  </si>
+  <si>
+    <t>Franklin</t>
+  </si>
+  <si>
+    <t>Wrigt</t>
+  </si>
+  <si>
+    <t>Alia</t>
+  </si>
+  <si>
+    <t>Thornton</t>
+  </si>
+  <si>
+    <t>Denzel</t>
+  </si>
+  <si>
+    <t>Flores</t>
+  </si>
+  <si>
+    <t>Bruno</t>
+  </si>
+  <si>
+    <t>Cordova</t>
+  </si>
+  <si>
+    <t>Jaylynn</t>
+  </si>
+  <si>
+    <t>Napp</t>
+  </si>
+  <si>
+    <t>Bruce</t>
+  </si>
+  <si>
+    <t>Rich</t>
+  </si>
+  <si>
+    <t>Arturo</t>
+  </si>
+  <si>
+    <t>Moore</t>
+  </si>
+  <si>
+    <t>Bryce</t>
+  </si>
+  <si>
+    <t>Carpenter</t>
+  </si>
+  <si>
+    <t>Jaidyn</t>
+  </si>
+  <si>
+    <t>Andersen</t>
+  </si>
+  <si>
+    <t>Mark</t>
+  </si>
+  <si>
+    <t>Walm</t>
+  </si>
+  <si>
+    <t>Harry</t>
+  </si>
+  <si>
+    <t>Lee</t>
+  </si>
+  <si>
+    <t>Josh</t>
+  </si>
+  <si>
+    <t>Johnson</t>
+  </si>
+  <si>
+    <t>Mik</t>
+  </si>
+  <si>
+    <t>Naam</t>
+  </si>
+  <si>
+    <t>First Name</t>
+  </si>
+  <si>
+    <t>Last Name</t>
   </si>
 </sst>
 </file>
@@ -337,7 +424,186 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="10">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="165" formatCode="0.0%"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0_);[Red]\(&quot;$&quot;#,##0\)"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -348,6 +614,26 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{3345C182-E1A4-429E-8610-51589ED4B994}" name="Table2" displayName="Table2" ref="A1:I29" totalsRowShown="0" headerRowDxfId="1">
+  <autoFilter ref="A1:I29" xr:uid="{3345C182-E1A4-429E-8610-51589ED4B994}"/>
+  <tableColumns count="9">
+    <tableColumn id="1" xr3:uid="{B9B44917-9487-4F7B-9EF3-896A746C8ED8}" name="Date" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{05A62D6F-FF9D-4E07-95A2-8F2FB2B6EA99}" name="Client" dataDxfId="8"/>
+    <tableColumn id="3" xr3:uid="{538B1C31-779B-4C18-BCF4-C3A9EFA57744}" name="First Name" dataDxfId="7"/>
+    <tableColumn id="11" xr3:uid="{80050487-B90E-480A-ACA0-E3E0858EED36}" name="Last Name" dataDxfId="0"/>
+    <tableColumn id="4" xr3:uid="{EBB16F0E-E759-43A7-8633-9F04E005AEDD}" name="Department" dataDxfId="6"/>
+    <tableColumn id="5" xr3:uid="{220E6ADA-E694-4163-9DBF-08FC92CC5416}" name="Payment" dataDxfId="5"/>
+    <tableColumn id="6" xr3:uid="{9B275C0E-06B0-4741-9F17-215C25A6B251}" name="Revenue" dataDxfId="4"/>
+    <tableColumn id="7" xr3:uid="{179DC0B4-DC20-4D1D-8AAB-0F89C227D0AF}" name="Profit" dataDxfId="3"/>
+    <tableColumn id="8" xr3:uid="{9A5D03BA-57E4-4D67-AF97-3FB2DC7C63AB}" name="Profit Margin" dataDxfId="2">
+      <calculatedColumnFormula>IFERROR(H2/G2,0)</calculatedColumnFormula>
+    </tableColumn>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -548,20 +834,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="42.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="17.19921875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.19921875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.09765625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.8984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="23" width="10.59765625" customWidth="1"/>
+    <col min="1" max="1" width="10.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.59765625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.5" customWidth="1"/>
+    <col min="5" max="5" width="17.19921875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.296875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.09765625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.59765625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16" bestFit="1" customWidth="1"/>
+    <col min="10" max="24" width="10.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="6" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" s="6" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -569,776 +857,863 @@
         <v>1</v>
       </c>
       <c r="C1" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="H1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="I1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>45076</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="1" t="s">
+      <c r="F2" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" s="3">
+      <c r="G2" s="3">
         <v>4500</v>
       </c>
-      <c r="G2" s="3">
+      <c r="H2" s="3">
         <v>598</v>
       </c>
-      <c r="H2" s="4">
-        <f>IFERROR(G2/F2,0)</f>
+      <c r="I2" s="4">
+        <f>IFERROR(H2/G2,0)</f>
         <v>0.13288888888888889</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>45076</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="3">
+      <c r="G3" s="3">
         <v>3800</v>
       </c>
-      <c r="G3" s="3">
+      <c r="H3" s="3">
         <v>1045</v>
       </c>
-      <c r="H3" s="4">
-        <f t="shared" ref="H3:H29" si="0">IFERROR(G3/F3,0)</f>
+      <c r="I3" s="4">
+        <f t="shared" ref="I3:I29" si="0">IFERROR(H3/G3,0)</f>
         <v>0.27500000000000002</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>45076</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="7">
+        <v>48</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="7">
         <v>0</v>
       </c>
-      <c r="F4" s="3">
+      <c r="G4" s="3">
         <v>3712.5</v>
       </c>
-      <c r="G4" s="3">
+      <c r="H4" s="3">
         <v>1009</v>
       </c>
-      <c r="H4" s="4">
+      <c r="I4" s="4">
         <f t="shared" si="0"/>
         <v>0.2717845117845118</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>45076</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5">
+      <c r="F5">
         <v>0</v>
       </c>
-      <c r="F5" s="3">
+      <c r="G5" s="3">
         <v>0</v>
       </c>
-      <c r="G5" s="3">
+      <c r="H5" s="3">
         <v>779</v>
       </c>
-      <c r="H5" s="4">
+      <c r="I5" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>45076</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F6" s="3">
+      <c r="G6" s="3">
         <v>5000</v>
       </c>
-      <c r="G6" s="3">
+      <c r="H6" s="3">
         <v>684</v>
       </c>
-      <c r="H6" s="4">
+      <c r="I6" s="4">
         <f t="shared" si="0"/>
         <v>0.1368</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>45077</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" s="3">
+      <c r="G7" s="3">
         <v>6100</v>
       </c>
-      <c r="G7" s="3">
+      <c r="H7" s="3">
         <v>544</v>
       </c>
-      <c r="H7" s="4">
+      <c r="I7" s="4">
         <f t="shared" si="0"/>
         <v>8.9180327868852466E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>45077</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4625</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>670</v>
       </c>
-      <c r="H8" s="4">
+      <c r="I8" s="4">
         <f t="shared" si="0"/>
         <v>0.14486486486486486</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>45077</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D9" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>3800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2045</v>
       </c>
-      <c r="H9" s="4">
+      <c r="I9" s="4">
         <f t="shared" si="0"/>
         <v>0.53815789473684206</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>45077</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" s="3">
+        <v>8</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G10" s="3">
         <v>3600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1564</v>
       </c>
-      <c r="H10" s="4">
+      <c r="I10" s="4">
         <f t="shared" si="0"/>
         <v>0.43444444444444447</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>45077</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>27</v>
+        <v>61</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>9</v>
+        <v>62</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F11" s="3">
+        <v>8</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" s="3">
         <v>5100</v>
       </c>
-      <c r="G11" s="3">
+      <c r="H11" s="3">
         <v>1220</v>
       </c>
-      <c r="H11" s="4">
+      <c r="I11" s="4">
         <f t="shared" si="0"/>
         <v>0.23921568627450981</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>45077</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F12" s="3">
+        <v>8</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" s="3">
         <v>4750</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>1435</v>
       </c>
-      <c r="H12" s="4">
+      <c r="I12" s="4">
         <f t="shared" si="0"/>
         <v>0.30210526315789471</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>45077</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>17</v>
+        <v>66</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" s="3">
+        <v>15</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G13" s="3">
         <v>6000</v>
       </c>
-      <c r="G13" s="3">
+      <c r="H13" s="3">
         <v>998</v>
       </c>
-      <c r="H13" s="4">
+      <c r="I13" s="4">
         <f t="shared" si="0"/>
         <v>0.16633333333333333</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>45077</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>31</v>
+        <v>68</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F14" s="3">
+        <v>27</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="G14" s="3">
         <v>4500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>780</v>
       </c>
-      <c r="H14" s="4">
+      <c r="I14" s="4">
         <f t="shared" si="0"/>
         <v>0.17333333333333334</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>45078</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>31</v>
+        <v>70</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F15" s="3">
+        <v>27</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" s="3">
         <v>0</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>1044</v>
       </c>
-      <c r="H15" s="4">
+      <c r="I15" s="4">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>45078</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" s="3">
+        <v>27</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G16" s="3">
         <v>3712.5</v>
       </c>
-      <c r="G16" s="3">
+      <c r="H16" s="3">
         <v>1222</v>
       </c>
-      <c r="H16" s="4">
+      <c r="I16" s="4">
         <f t="shared" si="0"/>
         <v>0.32915824915824915</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>45078</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" s="3">
+        <v>27</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G17" s="3">
         <v>4950</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1065</v>
       </c>
-      <c r="H17" s="4">
+      <c r="I17" s="4">
         <f t="shared" si="0"/>
         <v>0.21515151515151515</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>45078</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" s="3">
+        <v>15</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G18" s="3">
         <v>4750</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>810</v>
       </c>
-      <c r="H18" s="4">
+      <c r="I18" s="4">
         <f t="shared" si="0"/>
         <v>0.17052631578947369</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>45078</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" s="3">
+        <v>15</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G19" s="3">
         <v>7320</v>
       </c>
-      <c r="G19" s="3">
+      <c r="H19" s="3">
         <v>933</v>
       </c>
-      <c r="H19" s="4">
+      <c r="I19" s="4">
         <f t="shared" si="0"/>
         <v>0.12745901639344262</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>45078</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>31</v>
+        <v>80</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" s="3">
+        <v>27</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G20" s="3">
         <v>5087.5</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>655</v>
       </c>
-      <c r="H20" s="4">
+      <c r="I20" s="4">
         <f t="shared" si="0"/>
         <v>0.12874692874692875</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>45078</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F21" s="3">
+        <v>27</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G21" s="3">
         <v>4500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>722</v>
       </c>
-      <c r="H21" s="4">
+      <c r="I21" s="4">
         <f t="shared" si="0"/>
         <v>0.16044444444444445</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>45078</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>31</v>
+        <v>84</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F22" s="3">
+        <v>27</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G22" s="3">
         <v>4250</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>901</v>
       </c>
-      <c r="H22" s="4">
+      <c r="I22" s="4">
         <f t="shared" si="0"/>
         <v>0.21199999999999999</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>45079</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>31</v>
+        <v>86</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F23" s="3">
+        <v>27</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23" s="3">
         <v>5250</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1349</v>
       </c>
-      <c r="H23" s="4">
+      <c r="I23" s="4">
         <f t="shared" si="0"/>
         <v>0.25695238095238093</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>45079</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="D24" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F24" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E24" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>6500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>1288</v>
       </c>
-      <c r="H24" s="4">
+      <c r="I24" s="4">
         <f t="shared" si="0"/>
         <v>0.19815384615384615</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>45079</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>68</v>
+        <v>89</v>
       </c>
       <c r="D25" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F25" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E25" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="F25" s="3">
+      <c r="G25" s="3">
         <v>7500</v>
       </c>
-      <c r="G25" s="3">
+      <c r="H25" s="3">
         <v>1664</v>
       </c>
-      <c r="H25" s="4">
+      <c r="I25" s="4">
         <f t="shared" si="0"/>
         <v>0.22186666666666666</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>45079</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>12</v>
+        <v>92</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F26" s="3">
+        <v>11</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G26" s="3">
         <v>5500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1320</v>
       </c>
-      <c r="H26" s="4">
+      <c r="I26" s="4">
         <f t="shared" si="0"/>
         <v>0.24</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>45079</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>70</v>
+        <v>93</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>12</v>
+        <v>94</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F27" s="3">
+        <v>11</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G27" s="3">
         <v>4625</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1001</v>
       </c>
-      <c r="H27" s="4">
+      <c r="I27" s="4">
         <f t="shared" si="0"/>
         <v>0.21643243243243243</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>45079</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>12</v>
+        <v>96</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="F28" s="3">
+        <v>11</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="G28" s="3">
         <v>4500</v>
       </c>
-      <c r="G28" s="3">
+      <c r="H28" s="3">
         <v>960</v>
       </c>
-      <c r="H28" s="4">
+      <c r="I28" s="4">
         <f t="shared" si="0"/>
         <v>0.21333333333333335</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>45079</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>48</v>
+        <v>97</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>12</v>
+        <v>98</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F29" s="3">
+        <v>11</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G29" s="3">
         <v>5400</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>540</v>
       </c>
-      <c r="H29" s="4">
+      <c r="I29" s="4">
         <f t="shared" si="0"/>
         <v>0.1</v>
       </c>
@@ -1347,5 +1722,8 @@
   <dataConsolidate/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>